--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{571E9BBF-0DA6-43D3-89BF-7B08D7F22269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36503D06-68EB-4113-B67F-8E9E300BDE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="25365" windowHeight="15345" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="query" sheetId="1" r:id="rId1"/>
@@ -3237,6 +3237,7 @@
     <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8901,20 +8902,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8936,6 +8937,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -8949,12 +8958,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kladnik\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36503D06-68EB-4113-B67F-8E9E300BDE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AFA0A16-1CB6-4F13-81E6-29F99FD68986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="25365" windowHeight="15345" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="query" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="745">
   <si>
     <t>Kratica</t>
   </si>
@@ -2172,9 +2172,6 @@
     <t>Univerza</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t xml:space="preserve">mesečni pavšal </t>
   </si>
   <si>
@@ -2260,6 +2257,15 @@
   </si>
   <si>
     <t>55</t>
+  </si>
+  <si>
+    <t>ul</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>240</t>
   </si>
 </sst>
 </file>
@@ -2420,7 +2426,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2600,6 +2606,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2761,9 +2773,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2865,7 +2878,7 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="query" backgroundRefresh="0" connectionId="1" xr16:uid="{810FAF0E-E978-4166-990E-3191A3A52EB8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="20" unboundColumnsRight="5">
+  <queryTableRefresh nextId="21" unboundColumnsRight="5">
     <queryTableFields count="10">
       <queryTableField id="1" name="Kratica" tableColumnId="1"/>
       <queryTableField id="6" name="Naziv" tableColumnId="2"/>
@@ -2902,11 +2915,11 @@
     <tableColumn id="3" xr3:uid="{7DBEAD10-620D-4808-9B42-3A4FC4CD01F1}" uniqueName="Naslov" name="Naslov" queryTableFieldId="7" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{3B2C2683-BD51-4CEE-B257-9709DC3D05CF}" uniqueName="Po_x005f_x0161_ta" name="Pošta" queryTableFieldId="8" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{31B89103-3757-4829-A23D-5326180B058D}" uniqueName="ID_x005f_x0020_za_x005f_x0020_DDV" name="ID za DDV" queryTableFieldId="9" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{4682F1DC-6FFA-40BA-9223-F112B90F7B4E}" uniqueName="15" name="Univerza" queryTableFieldId="15" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{278777A9-EF9C-49A6-9267-A12ED1983808}" uniqueName="16" name="mesečni pavšal " queryTableFieldId="16" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{FF8E244F-138E-4296-8226-E347DBF40D15}" uniqueName="17" name="Dt" queryTableFieldId="17" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{0CA3CEF2-E5AD-4C18-8A5E-31053C947A6E}" uniqueName="18" name="Di" queryTableFieldId="18" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{8EDCC032-3462-49F3-B9B2-F02A4DB39366}" uniqueName="20" name="gostovanj" queryTableFieldId="19" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{4682F1DC-6FFA-40BA-9223-F112B90F7B4E}" uniqueName="15" name="Univerza" queryTableFieldId="15" dataDxfId="0"/>
+    <tableColumn id="16" xr3:uid="{278777A9-EF9C-49A6-9267-A12ED1983808}" uniqueName="16" name="mesečni pavšal " queryTableFieldId="16" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{FF8E244F-138E-4296-8226-E347DBF40D15}" uniqueName="17" name="Dt" queryTableFieldId="17" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{0CA3CEF2-E5AD-4C18-8A5E-31053C947A6E}" uniqueName="18" name="Di" queryTableFieldId="18" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{8EDCC032-3462-49F3-B9B2-F02A4DB39366}" uniqueName="20" name="gostovanj" queryTableFieldId="19" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3261,16 +3274,16 @@
         <v>712</v>
       </c>
       <c r="G1" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1" t="s">
         <v>714</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>715</v>
       </c>
-      <c r="I1" t="s">
-        <v>716</v>
-      </c>
       <c r="J1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3291,13 +3304,13 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -3361,16 +3374,16 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -3385,13 +3398,13 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -3410,7 +3423,7 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -3434,7 +3447,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -3458,7 +3471,7 @@
         <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -3475,9 +3488,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -3655,13 +3666,13 @@
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -3683,13 +3694,13 @@
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J20" s="1"/>
     </row>
@@ -3865,7 +3876,9 @@
       <c r="E29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>742</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -3925,13 +3938,13 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J32" s="1"/>
     </row>
@@ -4176,7 +4189,7 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4459,13 +4472,13 @@
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J59" s="1"/>
     </row>
@@ -4486,7 +4499,7 @@
         <v>179</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -4509,9 +4522,7 @@
       <c r="E61" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -4534,7 +4545,7 @@
         <v>185</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -4575,9 +4586,7 @@
         <v>22</v>
       </c>
       <c r="E64" s="1"/>
-      <c r="F64" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -4600,7 +4609,7 @@
         <v>193</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -4624,7 +4633,7 @@
         <v>196</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -4664,7 +4673,7 @@
         <v>200</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -4725,9 +4734,7 @@
       <c r="E71" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4769,7 +4776,9 @@
       <c r="E73" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>743</v>
+      </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -4792,7 +4801,7 @@
         <v>215</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -4838,7 +4847,7 @@
         <v>223</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -4859,9 +4868,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -4904,7 +4911,7 @@
         <v>230</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -4928,7 +4935,7 @@
         <v>233</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -4952,7 +4959,7 @@
         <v>236</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -5020,7 +5027,7 @@
         <v>200</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -5109,7 +5116,9 @@
       <c r="E88" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>743</v>
+      </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -5152,7 +5161,7 @@
         <v>261</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -5213,9 +5222,7 @@
       <c r="E93" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -5441,16 +5448,16 @@
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -5529,13 +5536,13 @@
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J108" s="1"/>
     </row>
@@ -5591,13 +5598,13 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J111" s="1"/>
     </row>
@@ -5841,13 +5848,13 @@
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J123" s="1"/>
     </row>
@@ -5867,9 +5874,7 @@
       <c r="E124" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F124" s="1"/>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -5975,13 +5980,13 @@
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J129" s="1"/>
     </row>
@@ -6221,13 +6226,13 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J141" s="1"/>
     </row>
@@ -6268,7 +6273,7 @@
         <v>415</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -6389,13 +6394,13 @@
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J149" s="1"/>
     </row>
@@ -6522,7 +6527,7 @@
         <v>446</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
@@ -6547,13 +6552,13 @@
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J157" s="1"/>
     </row>
@@ -6593,9 +6598,7 @@
       <c r="E159" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F159" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F159" s="1"/>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
@@ -6617,9 +6620,7 @@
       <c r="E160" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F160" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F160" s="1"/>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
@@ -6757,13 +6758,13 @@
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J167" s="1"/>
     </row>
@@ -6783,13 +6784,13 @@
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J168" s="1"/>
     </row>
@@ -6851,16 +6852,16 @@
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -6960,7 +6961,7 @@
         <v>200</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>640</v>
+        <v>743</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -6984,7 +6985,7 @@
         <v>502</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
@@ -7142,7 +7143,7 @@
         <v>523</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
@@ -7305,13 +7306,13 @@
       </c>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J193" s="1"/>
     </row>
@@ -7467,13 +7468,13 @@
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J201" s="1"/>
     </row>
@@ -7637,13 +7638,13 @@
       </c>
       <c r="F209" s="1"/>
       <c r="G209" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I209" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>718</v>
       </c>
       <c r="J209" s="1"/>
     </row>
@@ -7729,13 +7730,13 @@
       </c>
       <c r="F213" s="1"/>
       <c r="G213" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="H213" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="H213" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="I213" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J213" s="1"/>
     </row>
@@ -7798,7 +7799,7 @@
         <v>610</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
@@ -7821,13 +7822,13 @@
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J217" s="1"/>
     </row>
@@ -7885,16 +7886,16 @@
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -7972,7 +7973,7 @@
         <v>200</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
@@ -7991,13 +7992,13 @@
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="J225" s="1"/>
     </row>
@@ -8038,7 +8039,7 @@
       </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G227" s="1"/>
       <c r="H227" s="1"/>
@@ -8060,7 +8061,7 @@
       </c>
       <c r="E228" s="1"/>
       <c r="F228" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
@@ -8082,7 +8083,7 @@
       </c>
       <c r="E229" s="1"/>
       <c r="F229" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G229" s="1"/>
       <c r="H229" s="1"/>
@@ -8102,7 +8103,7 @@
       </c>
       <c r="E230" s="1"/>
       <c r="F230" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
@@ -8119,20 +8120,18 @@
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
-      <c r="F231" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F231" s="1"/>
       <c r="G231" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -8151,7 +8150,9 @@
       <c r="E232" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F232" s="1"/>
+      <c r="F232" s="1" t="s">
+        <v>743</v>
+      </c>
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
       <c r="I232" s="1"/>
@@ -8316,7 +8317,7 @@
         <v>665</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
@@ -8341,13 +8342,13 @@
       </c>
       <c r="F241" s="1"/>
       <c r="G241" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J241" s="1"/>
     </row>
@@ -8413,9 +8414,7 @@
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
-      <c r="F245" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F245" s="1"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
@@ -8435,9 +8434,7 @@
         <v>22</v>
       </c>
       <c r="E246" s="1"/>
-      <c r="F246" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F246" s="1"/>
       <c r="G246" s="1"/>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
@@ -8459,9 +8456,7 @@
       <c r="E247" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="F247" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="F247" s="1"/>
       <c r="G247" s="1"/>
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
@@ -8521,16 +8516,16 @@
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -8551,13 +8546,13 @@
       </c>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J251" s="1"/>
     </row>
@@ -8577,13 +8572,13 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J252" s="1"/>
     </row>
@@ -8676,7 +8671,7 @@
         <v>704</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>640</v>
+        <v>742</v>
       </c>
       <c r="G257" s="1"/>
       <c r="H257" s="1"/>
@@ -8699,7 +8694,7 @@
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>

--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kladnik\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AFA0A16-1CB6-4F13-81E6-29F99FD68986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA954D95-EB06-4F65-AEF5-AFD77D32854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="746">
   <si>
     <t>Kratica</t>
   </si>
@@ -2266,6 +2266,9 @@
   </si>
   <si>
     <t>240</t>
+  </si>
+  <si>
+    <t>64</t>
   </si>
 </sst>
 </file>
@@ -2915,11 +2918,11 @@
     <tableColumn id="3" xr3:uid="{7DBEAD10-620D-4808-9B42-3A4FC4CD01F1}" uniqueName="Naslov" name="Naslov" queryTableFieldId="7" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{3B2C2683-BD51-4CEE-B257-9709DC3D05CF}" uniqueName="Po_x005f_x0161_ta" name="Pošta" queryTableFieldId="8" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{31B89103-3757-4829-A23D-5326180B058D}" uniqueName="ID_x005f_x0020_za_x005f_x0020_DDV" name="ID za DDV" queryTableFieldId="9" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{4682F1DC-6FFA-40BA-9223-F112B90F7B4E}" uniqueName="15" name="Univerza" queryTableFieldId="15" dataDxfId="0"/>
-    <tableColumn id="16" xr3:uid="{278777A9-EF9C-49A6-9267-A12ED1983808}" uniqueName="16" name="mesečni pavšal " queryTableFieldId="16" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{FF8E244F-138E-4296-8226-E347DBF40D15}" uniqueName="17" name="Dt" queryTableFieldId="17" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{0CA3CEF2-E5AD-4C18-8A5E-31053C947A6E}" uniqueName="18" name="Di" queryTableFieldId="18" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{8EDCC032-3462-49F3-B9B2-F02A4DB39366}" uniqueName="20" name="gostovanj" queryTableFieldId="19" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{4682F1DC-6FFA-40BA-9223-F112B90F7B4E}" uniqueName="15" name="Univerza" queryTableFieldId="15" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{278777A9-EF9C-49A6-9267-A12ED1983808}" uniqueName="16" name="mesečni pavšal " queryTableFieldId="16" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{FF8E244F-138E-4296-8226-E347DBF40D15}" uniqueName="17" name="Dt" queryTableFieldId="17" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{0CA3CEF2-E5AD-4C18-8A5E-31053C947A6E}" uniqueName="18" name="Di" queryTableFieldId="18" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{8EDCC032-3462-49F3-B9B2-F02A4DB39366}" uniqueName="20" name="gostovanj" queryTableFieldId="19" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3426,8 +3429,12 @@
         <v>742</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -3450,8 +3457,12 @@
         <v>742</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -3474,8 +3485,12 @@
         <v>742</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3880,8 +3895,12 @@
         <v>742</v>
       </c>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="H29" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4502,8 +4521,12 @@
         <v>742</v>
       </c>
       <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
+      <c r="H60" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -4548,8 +4571,12 @@
         <v>742</v>
       </c>
       <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
+      <c r="H62" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -4612,8 +4639,12 @@
         <v>742</v>
       </c>
       <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+      <c r="H65" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4636,8 +4667,12 @@
         <v>742</v>
       </c>
       <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="H66" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -4676,8 +4711,12 @@
         <v>743</v>
       </c>
       <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+      <c r="H68" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -4780,8 +4819,12 @@
         <v>743</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="H73" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -4804,8 +4847,12 @@
         <v>742</v>
       </c>
       <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="H74" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -4850,8 +4897,12 @@
         <v>742</v>
       </c>
       <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
+      <c r="H76" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J76" s="1"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -4914,8 +4965,12 @@
         <v>742</v>
       </c>
       <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
+      <c r="H79" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J79" s="1"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -4938,8 +4993,12 @@
         <v>742</v>
       </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="H80" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J80" s="1"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -4962,8 +5021,12 @@
         <v>742</v>
       </c>
       <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
+      <c r="H81" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J81" s="1"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5030,8 +5093,12 @@
         <v>743</v>
       </c>
       <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
+      <c r="H84" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J84" s="1"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5120,8 +5187,12 @@
         <v>743</v>
       </c>
       <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
+      <c r="H88" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J88" s="1"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -5164,8 +5235,12 @@
         <v>742</v>
       </c>
       <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
+      <c r="H90" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J90" s="1"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6276,8 +6351,12 @@
         <v>742</v>
       </c>
       <c r="G143" s="1"/>
-      <c r="H143" s="1"/>
-      <c r="I143" s="1"/>
+      <c r="H143" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -6530,8 +6609,12 @@
         <v>742</v>
       </c>
       <c r="G156" s="1"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
+      <c r="H156" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J156" s="1"/>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -6964,8 +7047,12 @@
         <v>743</v>
       </c>
       <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
-      <c r="I176" s="1"/>
+      <c r="H176" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J176" s="1"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -6988,8 +7075,12 @@
         <v>742</v>
       </c>
       <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
-      <c r="I177" s="1"/>
+      <c r="H177" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J177" s="1"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -7146,8 +7237,12 @@
         <v>742</v>
       </c>
       <c r="G185" s="1"/>
-      <c r="H185" s="1"/>
-      <c r="I185" s="1"/>
+      <c r="H185" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J185" s="1"/>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -7802,8 +7897,12 @@
         <v>742</v>
       </c>
       <c r="G216" s="1"/>
-      <c r="H216" s="1"/>
-      <c r="I216" s="1"/>
+      <c r="H216" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J216" s="1"/>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -7976,8 +8075,12 @@
         <v>743</v>
       </c>
       <c r="G224" s="1"/>
-      <c r="H224" s="1"/>
-      <c r="I224" s="1"/>
+      <c r="H224" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J224" s="1"/>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -8042,8 +8145,12 @@
         <v>742</v>
       </c>
       <c r="G227" s="1"/>
-      <c r="H227" s="1"/>
-      <c r="I227" s="1"/>
+      <c r="H227" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J227" s="1"/>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -8064,8 +8171,12 @@
         <v>742</v>
       </c>
       <c r="G228" s="1"/>
-      <c r="H228" s="1"/>
-      <c r="I228" s="1"/>
+      <c r="H228" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J228" s="1"/>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -8086,8 +8197,12 @@
         <v>742</v>
       </c>
       <c r="G229" s="1"/>
-      <c r="H229" s="1"/>
-      <c r="I229" s="1"/>
+      <c r="H229" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J229" s="1"/>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -8106,8 +8221,12 @@
         <v>742</v>
       </c>
       <c r="G230" s="1"/>
-      <c r="H230" s="1"/>
-      <c r="I230" s="1"/>
+      <c r="H230" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J230" s="1"/>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -8154,8 +8273,12 @@
         <v>743</v>
       </c>
       <c r="G232" s="1"/>
-      <c r="H232" s="1"/>
-      <c r="I232" s="1"/>
+      <c r="H232" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J232" s="1"/>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -8320,8 +8443,12 @@
         <v>742</v>
       </c>
       <c r="G240" s="1"/>
-      <c r="H240" s="1"/>
-      <c r="I240" s="1"/>
+      <c r="H240" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J240" s="1"/>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -8674,8 +8801,12 @@
         <v>742</v>
       </c>
       <c r="G257" s="1"/>
-      <c r="H257" s="1"/>
-      <c r="I257" s="1"/>
+      <c r="H257" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>745</v>
+      </c>
       <c r="J257" s="1"/>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
@@ -8747,6 +8878,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B8424CE85351F64589369729664893D7" ma:contentTypeVersion="5" ma:contentTypeDescription="Ustvari nov dokument." ma:contentTypeScope="" ma:versionID="1ac781d2aabc82e157e45a1e96b6231b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44b6e255-9bec-4b65-ada2-b42ea9c0f358" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="79a5782f82df6e133ce65d5df1a4d33b" ns3:_="">
     <xsd:import namespace="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
@@ -8896,24 +9044,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EFA213E-BAB9-41D9-8FDD-B1DDC4C0B256}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8929,28 +9084,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA954D95-EB06-4F65-AEF5-AFD77D32854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B960CA-5565-4B66-B8D6-7885EA1ED480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="747">
   <si>
     <t>Kratica</t>
   </si>
@@ -2269,6 +2269,9 @@
   </si>
   <si>
     <t>64</t>
+  </si>
+  <si>
+    <t>vis</t>
   </si>
 </sst>
 </file>
@@ -3547,7 +3550,9 @@
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>746</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -8878,20 +8883,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9045,6 +9050,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -9056,14 +9069,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B960CA-5565-4B66-B8D6-7885EA1ED480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDDAC60-D913-4757-A317-BE5E4BDCB17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="748">
   <si>
     <t>Kratica</t>
   </si>
@@ -2272,6 +2272,9 @@
   </si>
   <si>
     <t>vis</t>
+  </si>
+  <si>
+    <t>VIS</t>
   </si>
 </sst>
 </file>
@@ -3334,7 +3337,9 @@
         <v>11</v>
       </c>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3506,7 +3511,9 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -3800,7 +3807,9 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -4386,7 +4395,9 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -4472,7 +4483,9 @@
       <c r="E58" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -4550,7 +4563,9 @@
       <c r="E61" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -4600,7 +4615,9 @@
       <c r="E63" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -4618,7 +4635,9 @@
         <v>22</v>
       </c>
       <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -4690,7 +4709,9 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -4734,7 +4755,9 @@
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -4756,7 +4779,9 @@
       <c r="E70" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -4778,7 +4803,9 @@
       <c r="E71" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4798,7 +4825,9 @@
         <v>210</v>
       </c>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -4876,7 +4905,9 @@
       <c r="E75" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F75" s="1"/>
+      <c r="F75" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -4924,7 +4955,9 @@
         <v>22</v>
       </c>
       <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -4944,7 +4977,9 @@
         <v>227</v>
       </c>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -5050,7 +5085,9 @@
       <c r="E82" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F82" s="1"/>
+      <c r="F82" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -5072,7 +5109,9 @@
       <c r="E83" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -5122,7 +5161,9 @@
       <c r="E85" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F85" s="1"/>
+      <c r="F85" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -5144,7 +5185,9 @@
       <c r="E86" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F86" s="1"/>
+      <c r="F86" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -5166,7 +5209,9 @@
       <c r="E87" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -5302,7 +5347,9 @@
       <c r="E93" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -5406,7 +5453,9 @@
       <c r="E98" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F98" s="1"/>
+      <c r="F98" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -5428,7 +5477,9 @@
       <c r="E99" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -5954,7 +6005,9 @@
       <c r="E124" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F124" s="1"/>
+      <c r="F124" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -6414,7 +6467,9 @@
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="1"/>
+      <c r="F146" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
@@ -6588,7 +6643,9 @@
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="1"/>
+      <c r="F155" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -6686,7 +6743,9 @@
       <c r="E159" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F159" s="1"/>
+      <c r="F159" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
@@ -6708,7 +6767,9 @@
       <c r="E160" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F160" s="1"/>
+      <c r="F160" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
@@ -7138,7 +7199,9 @@
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
+      <c r="F180" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -7806,7 +7869,9 @@
       <c r="E212" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F212" s="1"/>
+      <c r="F212" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -8300,7 +8365,9 @@
         <v>7</v>
       </c>
       <c r="E233" s="1"/>
-      <c r="F233" s="1"/>
+      <c r="F233" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
       <c r="I233" s="1"/>
@@ -8320,7 +8387,9 @@
         <v>218</v>
       </c>
       <c r="E234" s="1"/>
-      <c r="F234" s="1"/>
+      <c r="F234" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
@@ -8340,7 +8409,9 @@
         <v>218</v>
       </c>
       <c r="E235" s="1"/>
-      <c r="F235" s="1"/>
+      <c r="F235" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -8360,7 +8431,9 @@
         <v>218</v>
       </c>
       <c r="E236" s="1"/>
-      <c r="F236" s="1"/>
+      <c r="F236" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -8380,7 +8453,9 @@
         <v>218</v>
       </c>
       <c r="E237" s="1"/>
-      <c r="F237" s="1"/>
+      <c r="F237" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -8530,7 +8605,9 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
-      <c r="F244" s="1"/>
+      <c r="F244" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -8546,7 +8623,9 @@
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
-      <c r="F245" s="1"/>
+      <c r="F245" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
@@ -8566,7 +8645,9 @@
         <v>22</v>
       </c>
       <c r="E246" s="1"/>
-      <c r="F246" s="1"/>
+      <c r="F246" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G246" s="1"/>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
@@ -8588,7 +8669,9 @@
       <c r="E247" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="F247" s="1"/>
+      <c r="F247" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G247" s="1"/>
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
@@ -8604,7 +8687,9 @@
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
-      <c r="F248" s="1"/>
+      <c r="F248" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G248" s="1"/>
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
@@ -8626,7 +8711,9 @@
       <c r="E249" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="F249" s="1"/>
+      <c r="F249" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G249" s="1"/>
       <c r="H249" s="1"/>
       <c r="I249" s="1"/>
@@ -8724,7 +8811,9 @@
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
-      <c r="F253" s="1"/>
+      <c r="F253" s="1" t="s">
+        <v>747</v>
+      </c>
       <c r="G253" s="1"/>
       <c r="H253" s="1"/>
       <c r="I253" s="1"/>
@@ -8883,23 +8972,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B8424CE85351F64589369729664893D7" ma:contentTypeVersion="5" ma:contentTypeDescription="Ustvari nov dokument." ma:contentTypeScope="" ma:versionID="1ac781d2aabc82e157e45a1e96b6231b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44b6e255-9bec-4b65-ada2-b42ea9c0f358" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="79a5782f82df6e133ce65d5df1a4d33b" ns3:_="">
     <xsd:import namespace="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
@@ -9049,31 +9121,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EFA213E-BAB9-41D9-8FDD-B1DDC4C0B256}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9089,4 +9154,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDDAC60-D913-4757-A317-BE5E4BDCB17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBE66C2-D3E2-48F6-B02A-DA88A052FA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -3259,6 +3259,7 @@
     <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>

--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBE66C2-D3E2-48F6-B02A-DA88A052FA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AD371E-A6F5-43B4-9D28-75FC80C7B1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="749">
   <si>
     <t>Kratica</t>
   </si>
@@ -2275,6 +2275,9 @@
   </si>
   <si>
     <t>VIS</t>
+  </si>
+  <si>
+    <t>318</t>
   </si>
 </sst>
 </file>
@@ -3363,9 +3366,15 @@
         <v>15</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>718</v>
+      </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5961,9 +5970,15 @@
         <v>358</v>
       </c>
       <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
+      <c r="G122" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>718</v>
+      </c>
       <c r="J122" s="1"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -6723,9 +6738,15 @@
       </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
-      <c r="H158" s="1"/>
-      <c r="I158" s="1"/>
+      <c r="G158" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>718</v>
+      </c>
       <c r="J158" s="1"/>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9123,20 +9144,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9158,14 +9179,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -9179,4 +9192,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AC7E31-7FEC-4E33-B4AD-0631CB721870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD9A7F3-83F3-4D33-8D45-B9277101842A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="498">
   <si>
     <t>Kratica</t>
   </si>
@@ -653,9 +653,6 @@
   </si>
   <si>
     <t>ORTHODONTIO</t>
-  </si>
-  <si>
-    <t>OŠ Livade</t>
   </si>
   <si>
     <t>Osnovna Šola Livade Izola</t>
@@ -2634,34 +2631,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G1" t="s">
         <v>293</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I1" t="s">
         <v>294</v>
       </c>
-      <c r="H1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>295</v>
       </c>
-      <c r="J1" t="s">
-        <v>296</v>
-      </c>
       <c r="K1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2669,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -2678,18 +2675,18 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -2702,7 +2699,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -2711,22 +2708,22 @@
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G3" s="1">
         <v>350</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -2752,17 +2749,17 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="10"/>
@@ -2787,17 +2784,17 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="10"/>
@@ -2809,7 +2806,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>156</v>
@@ -2818,7 +2815,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -2846,22 +2843,22 @@
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -2878,7 +2875,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>20</v>
@@ -2887,19 +2884,19 @@
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -2925,19 +2922,19 @@
         <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2950,10 +2947,10 @@
         <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>30</v>
@@ -2962,23 +2959,23 @@
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="10"/>
@@ -3002,14 +2999,14 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -3022,10 +3019,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>34</v>
@@ -3035,14 +3032,14 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -3068,14 +3065,14 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -3091,28 +3088,28 @@
         <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -3134,7 +3131,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3164,19 +3161,19 @@
         <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -3186,30 +3183,30 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -3222,16 +3219,16 @@
         <v>51</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -3249,7 +3246,7 @@
         <v>54</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>45</v>
@@ -3258,22 +3255,22 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -3286,10 +3283,10 @@
         <v>55</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>53</v>
@@ -3298,19 +3295,19 @@
         <v>56</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -3323,7 +3320,7 @@
         <v>57</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>58</v>
@@ -3336,14 +3333,14 @@
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -3368,19 +3365,19 @@
         <v>62</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -3396,7 +3393,7 @@
         <v>63</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>20</v>
@@ -3405,10 +3402,10 @@
         <v>64</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -3416,7 +3413,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="1"/>
@@ -3438,19 +3435,19 @@
         <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -3463,10 +3460,10 @@
         <v>68</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>103</v>
@@ -3475,19 +3472,19 @@
         <v>69</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -3509,7 +3506,7 @@
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -3539,19 +3536,19 @@
         <v>73</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -3577,19 +3574,19 @@
         <v>76</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -3608,7 +3605,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -3637,17 +3634,17 @@
         <v>80</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -3660,31 +3657,31 @@
         <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -3701,7 +3698,7 @@
         <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>94</v>
@@ -3710,19 +3707,19 @@
         <v>83</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -3748,7 +3745,7 @@
         <v>86</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -3775,22 +3772,22 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -3816,17 +3813,17 @@
         <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -3852,19 +3849,19 @@
         <v>92</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -3881,7 +3878,7 @@
         <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>94</v>
@@ -3890,19 +3887,19 @@
         <v>95</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -3927,19 +3924,19 @@
         <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -3962,7 +3959,7 @@
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -3979,31 +3976,31 @@
         <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -4028,19 +4025,19 @@
         <v>106</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -4065,19 +4062,19 @@
         <v>109</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -4102,19 +4099,19 @@
         <v>112</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -4127,7 +4124,7 @@
         <v>113</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>114</v>
@@ -4139,25 +4136,25 @@
         <v>80</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O44" s="10"/>
     </row>
@@ -4169,7 +4166,7 @@
         <v>116</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>53</v>
@@ -4178,19 +4175,19 @@
         <v>117</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -4215,17 +4212,17 @@
         <v>80</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -4241,7 +4238,7 @@
         <v>120</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>121</v>
@@ -4250,19 +4247,19 @@
         <v>122</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -4276,7 +4273,7 @@
         <v>123</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
@@ -4288,19 +4285,19 @@
         <v>125</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -4314,10 +4311,10 @@
         <v>126</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>186</v>
@@ -4326,19 +4323,19 @@
         <v>127</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -4364,16 +4361,16 @@
         <v>80</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -4399,19 +4396,19 @@
         <v>132</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -4445,7 +4442,7 @@
         <v>134</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>135</v>
@@ -4457,26 +4454,26 @@
         <v>137</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P53" s="6"/>
     </row>
@@ -4485,7 +4482,7 @@
         <v>138</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>139</v>
@@ -4497,19 +4494,19 @@
         <v>140</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -4523,7 +4520,7 @@
         <v>141</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>139</v>
@@ -4535,19 +4532,19 @@
         <v>142</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -4561,7 +4558,7 @@
         <v>143</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>52</v>
@@ -4598,21 +4595,21 @@
         <v>148</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -4625,16 +4622,16 @@
         <v>149</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -4653,27 +4650,27 @@
         <v>150</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>151</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -4687,7 +4684,7 @@
         <v>152</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>153</v>
@@ -4696,18 +4693,18 @@
         <v>154</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -4721,7 +4718,7 @@
         <v>155</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>156</v>
@@ -4730,7 +4727,7 @@
         <v>7</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -4802,7 +4799,7 @@
         <v>163</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>164</v>
@@ -4811,7 +4808,7 @@
         <v>165</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -4830,7 +4827,7 @@
         <v>166</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>167</v>
@@ -4867,18 +4864,18 @@
         <v>7</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -4892,16 +4889,16 @@
         <v>173</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -4920,31 +4917,31 @@
         <v>174</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="H68" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -4961,7 +4958,7 @@
         <v>175</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>7</v>
@@ -4971,14 +4968,14 @@
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -4992,7 +4989,7 @@
         <v>177</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>178</v>
@@ -5001,18 +4998,18 @@
         <v>98</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -5038,19 +5035,19 @@
         <v>182</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -5064,31 +5061,31 @@
         <v>183</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="I72" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -5111,18 +5108,18 @@
         <v>7</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -5148,19 +5145,19 @@
         <v>189</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -5173,7 +5170,7 @@
         <v>190</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>191</v>
@@ -5182,18 +5179,18 @@
         <v>7</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -5218,14 +5215,14 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -5251,19 +5248,19 @@
         <v>189</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -5289,7 +5286,7 @@
         <v>189</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -5315,7 +5312,7 @@
         <v>154</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -5333,16 +5330,16 @@
         <v>199</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>200</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -5361,27 +5358,27 @@
         <v>201</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -5395,27 +5392,27 @@
         <v>202</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>154</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -5429,30 +5426,30 @@
         <v>203</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
@@ -5462,13 +5459,13 @@
     </row>
     <row r="84" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="C84" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>7</v>
@@ -5488,10 +5485,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>89</v>
@@ -5503,17 +5500,17 @@
         <v>80</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -5523,34 +5520,34 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -5560,34 +5557,34 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -5598,19 +5595,19 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>144</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
@@ -5627,34 +5624,34 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
@@ -5664,19 +5661,19 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -5692,10 +5689,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>156</v>
@@ -5704,7 +5701,7 @@
         <v>7</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
@@ -5720,10 +5717,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>39</v>
@@ -5732,18 +5729,18 @@
         <v>40</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -5754,28 +5751,28 @@
     </row>
     <row r="93" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="C93" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="D93" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>226</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -5785,19 +5782,19 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -5812,30 +5809,30 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
@@ -5846,10 +5843,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>156</v>
@@ -5858,19 +5855,19 @@
         <v>7</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
@@ -5880,19 +5877,19 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C97" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
@@ -5908,34 +5905,34 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -5945,30 +5942,30 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E99" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -5979,33 +5976,33 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
@@ -6015,32 +6012,32 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -6050,30 +6047,30 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>154</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -6084,34 +6081,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -6122,32 +6119,32 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C104" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -6157,32 +6154,32 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C105" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -6192,32 +6189,32 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C106" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6227,10 +6224,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>162</v>
@@ -6239,21 +6236,21 @@
         <v>7</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
@@ -6263,32 +6260,32 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -6299,10 +6296,10 @@
     </row>
     <row r="109" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>15</v>
@@ -6312,7 +6309,7 @@
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
@@ -6327,34 +6324,34 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="H110" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -6365,13 +6362,13 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>94</v>
@@ -6380,19 +6377,19 @@
         <v>36593346</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -6403,13 +6400,13 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>94</v>
@@ -6418,19 +6415,19 @@
         <v>34580492</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
@@ -6441,13 +6438,13 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>94</v>
@@ -6456,19 +6453,19 @@
         <v>82193592</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -6478,19 +6475,19 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F114" s="13"/>
       <c r="G114" s="1"/>
@@ -6505,34 +6502,34 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -6542,30 +6539,30 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
@@ -6575,34 +6572,34 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
@@ -6613,34 +6610,34 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
@@ -6651,34 +6648,34 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
@@ -6690,34 +6687,34 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
@@ -6729,34 +6726,34 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="F121" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="H121" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
@@ -6767,10 +6764,10 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>156</v>
@@ -6779,21 +6776,21 @@
         <v>7</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
@@ -6803,30 +6800,30 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="D123" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -6837,30 +6834,30 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
@@ -6871,34 +6868,34 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
@@ -6909,34 +6906,34 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -6946,23 +6943,23 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -6985,6 +6982,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B8424CE85351F64589369729664893D7" ma:contentTypeVersion="5" ma:contentTypeDescription="Ustvari nov dokument." ma:contentTypeScope="" ma:versionID="1ac781d2aabc82e157e45a1e96b6231b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44b6e255-9bec-4b65-ada2-b42ea9c0f358" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="79a5782f82df6e133ce65d5df1a4d33b" ns3:_="">
     <xsd:import namespace="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
@@ -7134,15 +7140,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7152,6 +7149,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EFA213E-BAB9-41D9-8FDD-B1DDC4C0B256}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7165,14 +7170,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD9A7F3-83F3-4D33-8D45-B9277101842A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E54DF5-7ADD-40A1-8BBD-4D9E42D031B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="497">
   <si>
     <t>Kratica</t>
   </si>
@@ -1415,9 +1415,6 @@
   </si>
   <si>
     <t>SI95535586</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SI71633065</t>
   </si>
   <si>
     <t>Univerza v Novem mestu, Fakulteta za ekonomijo in informatiko</t>
@@ -2806,7 +2803,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>156</v>
@@ -2815,7 +2812,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -3131,7 +3128,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3183,19 +3180,19 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>496</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
@@ -3460,7 +3457,7 @@
         <v>68</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>361</v>
@@ -3772,7 +3769,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>326</v>
@@ -4558,7 +4555,7 @@
         <v>143</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>52</v>
@@ -5419,6 +5416,10 @@
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
+      <c r="Q82">
+        <f>LEN(B83)</f>
+        <v>25</v>
+      </c>
       <c r="R82" s="6"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -5794,7 +5795,7 @@
         <v>98</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -6135,7 +6136,7 @@
         <v>322</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>324</v>
@@ -6170,7 +6171,7 @@
         <v>322</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>324</v>
@@ -6205,7 +6206,7 @@
         <v>322</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>324</v>
@@ -6272,7 +6273,7 @@
         <v>7</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>323</v>
@@ -6324,10 +6325,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>262</v>
@@ -6336,13 +6337,13 @@
         <v>94</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>326</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>324</v>
@@ -6362,10 +6363,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>262</v>
@@ -6400,10 +6401,10 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>262</v>
@@ -6438,10 +6439,10 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>262</v>
@@ -6456,7 +6457,7 @@
         <v>326</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>324</v>
@@ -6478,10 +6479,10 @@
         <v>263</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>168</v>
@@ -6578,13 +6579,13 @@
         <v>273</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>326</v>
@@ -6616,19 +6617,19 @@
         <v>274</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>326</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>324</v>
@@ -6651,7 +6652,7 @@
         <v>275</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>276</v>
@@ -6660,7 +6661,7 @@
         <v>20</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>326</v>
@@ -6693,19 +6694,19 @@
         <v>277</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>326</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>324</v>
@@ -6729,10 +6730,10 @@
         <v>278</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>244</v>
@@ -6744,7 +6745,7 @@
         <v>326</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>324</v>
@@ -6767,7 +6768,7 @@
         <v>280</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>156</v>
@@ -6776,7 +6777,7 @@
         <v>7</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
@@ -6812,7 +6813,7 @@
         <v>271</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
@@ -6846,7 +6847,7 @@
         <v>154</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
@@ -6871,16 +6872,16 @@
         <v>286</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>326</v>
@@ -6955,7 +6956,7 @@
         <v>154</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">

--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E54DF5-7ADD-40A1-8BBD-4D9E42D031B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CD5081-E1E5-47F5-AA57-438E6A329A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="495">
   <si>
     <t>Kratica</t>
   </si>
@@ -206,12 +206,6 @@
   </si>
   <si>
     <t>5000 Nova Gorica</t>
-  </si>
-  <si>
-    <t>EMUNI</t>
-  </si>
-  <si>
-    <t>EPF</t>
   </si>
   <si>
     <t>SI78769108</t>
@@ -2258,7 +2252,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A37B9E62-4060-4509-B0D0-60F912CE029E}" name="Table_query" displayName="Table_query" ref="A1:O127" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:O127" xr:uid="{A37B9E62-4060-4509-B0D0-60F912CE029E}"/>
+  <autoFilter ref="A1:O127" xr:uid="{A37B9E62-4060-4509-B0D0-60F912CE029E}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="VIS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{B3D59791-FB16-42CB-A5D4-2A3DA647622B}" uniqueName="Title" name="Kratica" queryTableFieldId="1" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{B7A63C42-317B-4372-8AF6-7B74693BE5F3}" uniqueName="Naziva" name="Naziv" queryTableFieldId="6" dataDxfId="13"/>
@@ -2628,42 +2628,42 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1" t="s">
+        <v>330</v>
+      </c>
+      <c r="I1" t="s">
         <v>292</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>293</v>
       </c>
-      <c r="H1" t="s">
-        <v>332</v>
-      </c>
-      <c r="I1" t="s">
-        <v>294</v>
-      </c>
-      <c r="J1" t="s">
-        <v>295</v>
-      </c>
       <c r="K1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="N1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -2672,18 +2672,18 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -2696,7 +2696,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -2705,22 +2705,22 @@
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G3" s="1">
         <v>350</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -2728,7 +2728,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -2746,24 +2746,24 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="10"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2781,38 +2781,38 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="10"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -2826,7 +2826,7 @@
       <c r="O6" s="1"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2840,22 +2840,22 @@
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -2864,7 +2864,7 @@
       <c r="O7" s="1"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>20</v>
@@ -2881,19 +2881,19 @@
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -2902,7 +2902,7 @@
       <c r="O8" s="1"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -2919,19 +2919,19 @@
         <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2944,10 +2944,10 @@
         <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>30</v>
@@ -2956,29 +2956,29 @@
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="10"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -3011,15 +3011,15 @@
       <c r="N11" s="10"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>34</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -3044,7 +3044,7 @@
       <c r="N12" s="10"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -3085,28 +3085,28 @@
         <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -3114,7 +3114,7 @@
       <c r="N14" s="10"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3141,7 +3141,7 @@
       <c r="N15" s="10"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -3158,19 +3158,19 @@
         <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -3178,32 +3178,32 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -3211,21 +3211,21 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -3239,11 +3239,11 @@
       <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>54</v>
+      <c r="A19" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>45</v>
@@ -3252,22 +3252,22 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -3276,35 +3276,35 @@
       <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>55</v>
+      <c r="A20" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -3312,32 +3312,32 @@
       <c r="N20" s="10"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -3345,36 +3345,36 @@
       <c r="N21" s="10"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -3384,25 +3384,25 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -3410,41 +3410,41 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -3454,34 +3454,34 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -3492,19 +3492,17 @@
     </row>
     <row r="26" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="7" t="s">
-        <v>326</v>
-      </c>
+      <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -3516,36 +3514,36 @@
       <c r="O26" s="7"/>
       <c r="P26" s="9"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -3554,36 +3552,36 @@
       <c r="O27" s="1"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -3593,16 +3591,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -3614,34 +3612,34 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -3651,34 +3649,34 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -3689,34 +3687,34 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -3727,23 +3725,21 @@
     </row>
     <row r="33" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -3757,10 +3753,10 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>9</v>
@@ -3769,22 +3765,22 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -3793,34 +3789,34 @@
       <c r="O34" s="10"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -3829,36 +3825,36 @@
       <c r="O35" s="1"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -3869,34 +3865,34 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -3904,36 +3900,36 @@
       <c r="N37" s="1"/>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -3943,21 +3939,19 @@
     </row>
     <row r="39" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="7"/>
-      <c r="F39" s="7" t="s">
-        <v>326</v>
-      </c>
+      <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -3970,34 +3964,34 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -4005,36 +3999,36 @@
       <c r="N40" s="1"/>
       <c r="O40" s="10"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -4042,36 +4036,36 @@
       <c r="N41" s="1"/>
       <c r="O41" s="10"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -4079,36 +4073,36 @@
       <c r="N42" s="1"/>
       <c r="O42" s="10"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -4116,75 +4110,75 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O44" s="10"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -4192,34 +4186,34 @@
       <c r="N45" s="1"/>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -4229,34 +4223,34 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -4267,34 +4261,34 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -4305,34 +4299,34 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="H49" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -4341,33 +4335,33 @@
       <c r="O49" s="1"/>
       <c r="P49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -4376,36 +4370,36 @@
       <c r="O50" s="1"/>
       <c r="P50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -4413,12 +4407,12 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -4436,74 +4430,74 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -4514,34 +4508,34 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -4550,21 +4544,21 @@
       <c r="O55" s="1"/>
       <c r="Q55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -4578,35 +4572,35 @@
       <c r="O56" s="1"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -4614,21 +4608,21 @@
       <c r="O57" s="1"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -4642,32 +4636,32 @@
       <c r="O58" s="1"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -4676,32 +4670,32 @@
       <c r="O59" s="1"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="E60" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -4710,21 +4704,21 @@
       <c r="O60" s="1"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -4738,21 +4732,21 @@
       <c r="O61" s="1"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="D62" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -4766,15 +4760,15 @@
       <c r="O62" s="1"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>7</v>
@@ -4791,21 +4785,21 @@
       <c r="N63" s="14"/>
       <c r="O63" s="14"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -4819,21 +4813,21 @@
       <c r="O64" s="1"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -4847,32 +4841,32 @@
       <c r="O65" s="1"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -4881,21 +4875,21 @@
       <c r="O66" s="1"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -4911,34 +4905,34 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -4947,32 +4941,32 @@
       <c r="O68" s="1"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -4981,32 +4975,32 @@
       <c r="O69" s="1"/>
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -5015,36 +5009,36 @@
       <c r="O70" s="1"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -5055,34 +5049,34 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="H72" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -5091,32 +5085,32 @@
       <c r="O72" s="1"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -5125,36 +5119,36 @@
       <c r="O73" s="1"/>
       <c r="Q73" s="6"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -5162,32 +5156,32 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -5196,15 +5190,15 @@
       <c r="O75" s="1"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>7</v>
@@ -5212,14 +5206,14 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -5230,34 +5224,34 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -5268,22 +5262,22 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -5295,21 +5289,21 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -5322,21 +5316,21 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -5350,32 +5344,32 @@
       <c r="O80" s="1"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -5384,32 +5378,32 @@
       <c r="O81" s="1"/>
       <c r="R81" s="6"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -5422,35 +5416,35 @@
       </c>
       <c r="R82" s="6"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
@@ -5458,15 +5452,15 @@
       <c r="O83" s="1"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C84" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>7</v>
@@ -5484,34 +5478,34 @@
       <c r="O84" s="7"/>
       <c r="Q84" s="9"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -5519,36 +5513,36 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -5558,34 +5552,34 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -5594,21 +5588,21 @@
       <c r="O87" s="1"/>
       <c r="P87" s="6"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
@@ -5623,36 +5617,36 @@
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
@@ -5660,21 +5654,21 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -5688,21 +5682,21 @@
       <c r="O90" s="1"/>
       <c r="R90" s="12"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
@@ -5716,12 +5710,12 @@
       <c r="O91" s="1"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>39</v>
@@ -5730,18 +5724,18 @@
         <v>40</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -5750,30 +5744,30 @@
       <c r="O92" s="1"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="D93" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>225</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -5781,21 +5775,21 @@
       <c r="N93" s="7"/>
       <c r="O93" s="7"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="D94" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -5808,32 +5802,32 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
@@ -5842,33 +5836,33 @@
       <c r="O95" s="1"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
@@ -5876,21 +5870,21 @@
       <c r="O96" s="1"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
@@ -5904,36 +5898,36 @@
       <c r="O97" s="1"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -5941,32 +5935,32 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E99" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -5975,35 +5969,35 @@
       <c r="O99" s="1"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
@@ -6011,34 +6005,34 @@
       <c r="O100" s="1"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -6046,32 +6040,32 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -6080,36 +6074,36 @@
       <c r="O102" s="1"/>
       <c r="Q102" s="12"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -6118,34 +6112,34 @@
       <c r="O103" s="1"/>
       <c r="Q103" s="6"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -6153,34 +6147,34 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -6188,34 +6182,34 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6223,35 +6217,35 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
@@ -6259,34 +6253,34 @@
       <c r="O107" s="1"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -6297,10 +6291,10 @@
     </row>
     <row r="109" spans="1:18" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>15</v>
@@ -6309,9 +6303,7 @@
         <v>7</v>
       </c>
       <c r="E109" s="14"/>
-      <c r="F109" s="14" t="s">
-        <v>326</v>
-      </c>
+      <c r="F109" s="14"/>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="14"/>
@@ -6325,34 +6317,34 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="H110" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -6363,34 +6355,34 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E111" s="1">
         <v>36593346</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -6401,34 +6393,34 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E112" s="1">
         <v>34580492</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
@@ -6439,34 +6431,34 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E113" s="1">
         <v>82193592</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -6474,21 +6466,21 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F114" s="13"/>
       <c r="G114" s="1"/>
@@ -6501,36 +6493,36 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -6538,32 +6530,32 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
@@ -6573,34 +6565,34 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
@@ -6611,34 +6603,34 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
@@ -6649,34 +6641,34 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
@@ -6688,34 +6680,34 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
@@ -6727,34 +6719,34 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="H121" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
@@ -6763,35 +6755,35 @@
       <c r="O121" s="1"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
@@ -6799,32 +6791,32 @@
       <c r="O122" s="1"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="D123" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -6833,32 +6825,32 @@
       <c r="O123" s="1"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
@@ -6869,34 +6861,34 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
@@ -6905,36 +6897,36 @@
       <c r="O125" s="1"/>
       <c r="Q125" s="6"/>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -6942,25 +6934,25 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -6983,12 +6975,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7142,17 +7133,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7176,17 +7176,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CD5081-E1E5-47F5-AA57-438E6A329A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF58EF7-DB09-49C9-BF64-BE947CEF21B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -2252,13 +2252,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A37B9E62-4060-4509-B0D0-60F912CE029E}" name="Table_query" displayName="Table_query" ref="A1:O127" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:O127" xr:uid="{A37B9E62-4060-4509-B0D0-60F912CE029E}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="VIS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O127" xr:uid="{A37B9E62-4060-4509-B0D0-60F912CE029E}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{B3D59791-FB16-42CB-A5D4-2A3DA647622B}" uniqueName="Title" name="Kratica" queryTableFieldId="1" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{B7A63C42-317B-4372-8AF6-7B74693BE5F3}" uniqueName="Naziva" name="Naziv" queryTableFieldId="6" dataDxfId="13"/>
@@ -2658,7 +2652,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2728,7 +2722,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -2763,7 +2757,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2798,7 +2792,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -2826,7 +2820,7 @@
       <c r="O6" s="1"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2864,7 +2858,7 @@
       <c r="O7" s="1"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -2902,7 +2896,7 @@
       <c r="O8" s="1"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -2978,7 +2972,7 @@
       <c r="N10" s="10"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -3011,7 +3005,7 @@
       <c r="N11" s="10"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -3044,7 +3038,7 @@
       <c r="N12" s="10"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -3114,7 +3108,7 @@
       <c r="N14" s="10"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
@@ -3141,7 +3135,7 @@
       <c r="N15" s="10"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -3178,7 +3172,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>492</v>
       </c>
@@ -3211,7 +3205,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
@@ -3312,7 +3306,7 @@
       <c r="N20" s="10"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
@@ -3345,7 +3339,7 @@
       <c r="N21" s="10"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -3415,7 +3409,7 @@
       <c r="N23" s="10"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
@@ -3514,7 +3508,7 @@
       <c r="O26" s="7"/>
       <c r="P26" s="9"/>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>69</v>
       </c>
@@ -3552,7 +3546,7 @@
       <c r="O27" s="1"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>72</v>
       </c>
@@ -3612,7 +3606,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>76</v>
       </c>
@@ -3789,7 +3783,7 @@
       <c r="O34" s="10"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>86</v>
       </c>
@@ -3825,7 +3819,7 @@
       <c r="O35" s="1"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>88</v>
       </c>
@@ -3900,7 +3894,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>94</v>
       </c>
@@ -3999,7 +3993,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="10"/>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>102</v>
       </c>
@@ -4036,7 +4030,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="10"/>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>105</v>
       </c>
@@ -4073,7 +4067,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="10"/>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>108</v>
       </c>
@@ -4110,7 +4104,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>111</v>
       </c>
@@ -4186,7 +4180,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>116</v>
       </c>
@@ -4335,7 +4329,7 @@
       <c r="O49" s="1"/>
       <c r="P49" s="6"/>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>126</v>
       </c>
@@ -4370,7 +4364,7 @@
       <c r="O50" s="1"/>
       <c r="P50" s="6"/>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>128</v>
       </c>
@@ -4407,7 +4401,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:17" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>131</v>
       </c>
@@ -4544,7 +4538,7 @@
       <c r="O55" s="1"/>
       <c r="Q55" s="6"/>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>141</v>
       </c>
@@ -4572,7 +4566,7 @@
       <c r="O56" s="1"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>144</v>
       </c>
@@ -4608,7 +4602,7 @@
       <c r="O57" s="1"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
@@ -4636,7 +4630,7 @@
       <c r="O58" s="1"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>148</v>
       </c>
@@ -4670,7 +4664,7 @@
       <c r="O59" s="1"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>150</v>
       </c>
@@ -4704,7 +4698,7 @@
       <c r="O60" s="1"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>153</v>
       </c>
@@ -4732,7 +4726,7 @@
       <c r="O61" s="1"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>155</v>
       </c>
@@ -4760,7 +4754,7 @@
       <c r="O62" s="1"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>159</v>
       </c>
@@ -4785,7 +4779,7 @@
       <c r="N63" s="14"/>
       <c r="O63" s="14"/>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>161</v>
       </c>
@@ -4813,7 +4807,7 @@
       <c r="O64" s="1"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>164</v>
       </c>
@@ -4841,7 +4835,7 @@
       <c r="O65" s="1"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>168</v>
       </c>
@@ -4875,7 +4869,7 @@
       <c r="O66" s="1"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>171</v>
       </c>
@@ -4941,7 +4935,7 @@
       <c r="O68" s="1"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>173</v>
       </c>
@@ -4975,7 +4969,7 @@
       <c r="O69" s="1"/>
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>175</v>
       </c>
@@ -5009,7 +5003,7 @@
       <c r="O70" s="1"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>177</v>
       </c>
@@ -5085,7 +5079,7 @@
       <c r="O72" s="1"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>182</v>
       </c>
@@ -5119,7 +5113,7 @@
       <c r="O73" s="1"/>
       <c r="Q73" s="6"/>
     </row>
-    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>185</v>
       </c>
@@ -5156,7 +5150,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>188</v>
       </c>
@@ -5190,7 +5184,7 @@
       <c r="O75" s="1"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>190</v>
       </c>
@@ -5289,7 +5283,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>195</v>
       </c>
@@ -5316,7 +5310,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>197</v>
       </c>
@@ -5344,7 +5338,7 @@
       <c r="O80" s="1"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>199</v>
       </c>
@@ -5378,7 +5372,7 @@
       <c r="O81" s="1"/>
       <c r="R81" s="6"/>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>200</v>
       </c>
@@ -5416,7 +5410,7 @@
       </c>
       <c r="R82" s="6"/>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>201</v>
       </c>
@@ -5452,7 +5446,7 @@
       <c r="O83" s="1"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:18" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>204</v>
       </c>
@@ -5478,7 +5472,7 @@
       <c r="O84" s="7"/>
       <c r="Q84" s="9"/>
     </row>
-    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>207</v>
       </c>
@@ -5513,7 +5507,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>208</v>
       </c>
@@ -5588,7 +5582,7 @@
       <c r="O87" s="1"/>
       <c r="P87" s="6"/>
     </row>
-    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>212</v>
       </c>
@@ -5617,7 +5611,7 @@
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
-    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>214</v>
       </c>
@@ -5654,7 +5648,7 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>217</v>
       </c>
@@ -5682,7 +5676,7 @@
       <c r="O90" s="1"/>
       <c r="R90" s="12"/>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>440</v>
       </c>
@@ -5710,7 +5704,7 @@
       <c r="O91" s="1"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>218</v>
       </c>
@@ -5744,7 +5738,7 @@
       <c r="O92" s="1"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:18" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>220</v>
       </c>
@@ -5775,7 +5769,7 @@
       <c r="N93" s="7"/>
       <c r="O93" s="7"/>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>224</v>
       </c>
@@ -5802,7 +5796,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>227</v>
       </c>
@@ -5836,7 +5830,7 @@
       <c r="O95" s="1"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>228</v>
       </c>
@@ -5870,7 +5864,7 @@
       <c r="O96" s="1"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>231</v>
       </c>
@@ -5898,7 +5892,7 @@
       <c r="O97" s="1"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>234</v>
       </c>
@@ -5935,7 +5929,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>237</v>
       </c>
@@ -5969,7 +5963,7 @@
       <c r="O99" s="1"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>241</v>
       </c>
@@ -6005,7 +5999,7 @@
       <c r="O100" s="1"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>243</v>
       </c>
@@ -6040,7 +6034,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>246</v>
       </c>
@@ -6074,7 +6068,7 @@
       <c r="O102" s="1"/>
       <c r="Q102" s="12"/>
     </row>
-    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>247</v>
       </c>
@@ -6112,7 +6106,7 @@
       <c r="O103" s="1"/>
       <c r="Q103" s="6"/>
     </row>
-    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>249</v>
       </c>
@@ -6147,7 +6141,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>251</v>
       </c>
@@ -6182,7 +6176,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>253</v>
       </c>
@@ -6217,7 +6211,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>255</v>
       </c>
@@ -6253,7 +6247,7 @@
       <c r="O107" s="1"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>257</v>
       </c>
@@ -6466,7 +6460,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>261</v>
       </c>
@@ -6493,7 +6487,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>263</v>
       </c>
@@ -6530,7 +6524,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>266</v>
       </c>
@@ -6755,7 +6749,7 @@
       <c r="O121" s="1"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>278</v>
       </c>
@@ -6791,7 +6785,7 @@
       <c r="O122" s="1"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>279</v>
       </c>
@@ -6825,7 +6819,7 @@
       <c r="O123" s="1"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>282</v>
       </c>
@@ -6897,7 +6891,7 @@
       <c r="O125" s="1"/>
       <c r="Q125" s="6"/>
     </row>
-    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>285</v>
       </c>
@@ -6934,7 +6928,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>288</v>
       </c>
@@ -6983,6 +6977,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B8424CE85351F64589369729664893D7" ma:contentTypeVersion="5" ma:contentTypeDescription="Ustvari nov dokument." ma:contentTypeScope="" ma:versionID="1ac781d2aabc82e157e45a1e96b6231b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44b6e255-9bec-4b65-ada2-b42ea9c0f358" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="79a5782f82df6e133ce65d5df1a4d33b" ns3:_="">
     <xsd:import namespace="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
@@ -7132,15 +7135,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
   <ds:schemaRefs>
@@ -7158,6 +7152,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EFA213E-BAB9-41D9-8FDD-B1DDC4C0B256}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7173,12 +7175,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assets/Stranke.xlsx
+++ b/assets/Stranke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF58EF7-DB09-49C9-BF64-BE947CEF21B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F9E391-5435-4053-A80E-BA349BE4C586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{54F47D17-901F-4DA7-82BF-452E61896D1B}"/>
   </bookViews>
@@ -6969,23 +6969,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B8424CE85351F64589369729664893D7" ma:contentTypeVersion="5" ma:contentTypeDescription="Ustvari nov dokument." ma:contentTypeScope="" ma:versionID="1ac781d2aabc82e157e45a1e96b6231b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44b6e255-9bec-4b65-ada2-b42ea9c0f358" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="79a5782f82df6e133ce65d5df1a4d33b" ns3:_="">
     <xsd:import namespace="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
@@ -7135,7 +7118,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44b6e255-9bec-4b65-ada2-b42ea9c0f358" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EFA213E-BAB9-41D9-8FDD-B1DDC4C0B256}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3560CBC-637F-42C1-B146-9EED4519BB73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -7151,28 +7169,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF107626-ADC0-42BC-82E5-E38C6154BC12}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EFA213E-BAB9-41D9-8FDD-B1DDC4C0B256}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44b6e255-9bec-4b65-ada2-b42ea9c0f358"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>